--- a/htr-update-fr-medication/ig/StructureDefinition-fr-service-request-imaging-document.xlsx
+++ b/htr-update-fr-medication/ig/StructureDefinition-fr-service-request-imaging-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T08:28:14+00:00</t>
+    <t>2026-09-04T09:33:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -5827,7 +5827,7 @@
         <v>80</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>81</v>
+        <v>147</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>141</v>
@@ -5946,7 +5946,7 @@
         <v>80</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>81</v>
+        <v>147</v>
       </c>
       <c r="AJ32" t="s" s="2">
         <v>141</v>
@@ -8744,7 +8744,7 @@
         <v>80</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>81</v>
+        <v>147</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>141</v>
